--- a/src/main/java/resources/tasks.xlsx
+++ b/src/main/java/resources/tasks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Java\projectStart\projectStart\src\main\java\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE247AB1-2242-4B10-93A2-8EE18902A013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F08D140-0964-4C36-ADB1-316E14621BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9135" yWindow="2175" windowWidth="14640" windowHeight="10410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>id</t>
   </si>
@@ -58,6 +58,9 @@
   </si>
   <si>
     <t>Съесть торт</t>
+  </si>
+  <si>
+    <t>projectId</t>
   </si>
 </sst>
 </file>
@@ -376,7 +379,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -384,7 +387,7 @@
     <col min="4" max="5" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -400,8 +403,11 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
@@ -417,8 +423,11 @@
       <c r="E2" s="1">
         <v>36527</v>
       </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -434,8 +443,11 @@
       <c r="E3" s="1">
         <v>40466</v>
       </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -450,6 +462,9 @@
       </c>
       <c r="E4" s="1">
         <v>40476</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
